--- a/data/stats/supp_tables/fallcover-soilcover-wea-estimates.xlsx
+++ b/data/stats/supp_tables/fallcover-soilcover-wea-estimates.xlsx
@@ -11,6 +11,38 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+  <si>
+    <t>weayear</t>
+  </si>
+  <si>
+    <t>response</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>asymp.LCL</t>
+  </si>
+  <si>
+    <t>asymp.UCL</t>
+  </si>
+  <si>
+    <t>dry-hot</t>
+  </si>
+  <si>
+    <t>Inf</t>
+  </si>
+  <si>
+    <t>wet-hot</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,84 +386,64 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>weayear</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>response</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>SE</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>df</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>asymp.LCL</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>asymp.UCL</t>
-        </is>
+    <row r="1" spans="1:6" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>dry-hot</t>
-        </is>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>0.7730524187371529</v>
+        <v>0.7730529618178114</v>
       </c>
       <c r="C2">
-        <v>0.01775920237966989</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.01775930312539393</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
       </c>
       <c r="E2">
-        <v>0.7363785015778455</v>
+        <v>0.7363788188990786</v>
       </c>
       <c r="F2">
-        <v>0.8059687396826399</v>
+        <v>0.805969452220926</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>wet-hot</t>
-        </is>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>8</v>
       </c>
       <c r="B3">
-        <v>0.7095596758494744</v>
+        <v>0.7095605112717763</v>
       </c>
       <c r="C3">
-        <v>0.02081937539728839</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.02081949411198741</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
       </c>
       <c r="E3">
-        <v>0.66713253092818</v>
+        <v>0.6671331057117069</v>
       </c>
       <c r="F3">
-        <v>0.7486167759530292</v>
+        <v>0.7486178146137545</v>
       </c>
     </row>
   </sheetData>
